--- a/ope勤務条件表_2026_4sheets.xlsx
+++ b/ope勤務条件表_2026_4sheets.xlsx
@@ -11,6 +11,7 @@
     <sheet name="シフト制約条件" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="手術スケジュール" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="前月シフト実績" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="設定" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -512,25 +513,10 @@
           <t>週5日</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v/>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>2026/12/29-2027/01/03</t>
         </is>
-      </c>
-      <c r="H2" t="n">
-        <v/>
-      </c>
-      <c r="I2" t="n">
-        <v/>
-      </c>
-      <c r="J2" t="n">
-        <v/>
-      </c>
-      <c r="K2" t="n">
-        <v/>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -567,25 +553,10 @@
           <t>週5日</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v/>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>2026/12/29-2027/01/03</t>
         </is>
-      </c>
-      <c r="H3" t="n">
-        <v/>
-      </c>
-      <c r="I3" t="n">
-        <v/>
-      </c>
-      <c r="J3" t="n">
-        <v/>
-      </c>
-      <c r="K3" t="n">
-        <v/>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -622,27 +593,15 @@
           <t>週5日</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v/>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="H4" t="n">
-        <v/>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>月曜出勤必須</t>
         </is>
-      </c>
-      <c r="J4" t="n">
-        <v/>
-      </c>
-      <c r="K4" t="n">
-        <v/>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -679,27 +638,15 @@
           <t>週5日</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v/>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="H5" t="n">
-        <v/>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>月曜出勤必須</t>
         </is>
-      </c>
-      <c r="J5" t="n">
-        <v/>
-      </c>
-      <c r="K5" t="n">
-        <v/>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -736,25 +683,10 @@
           <t>週5日</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v/>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>2026/12/29-2027/01/03</t>
         </is>
-      </c>
-      <c r="H6" t="n">
-        <v/>
-      </c>
-      <c r="I6" t="n">
-        <v/>
-      </c>
-      <c r="J6" t="n">
-        <v/>
-      </c>
-      <c r="K6" t="n">
-        <v/>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -801,18 +733,6 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="H7" t="n">
-        <v/>
-      </c>
-      <c r="I7" t="n">
-        <v/>
-      </c>
-      <c r="J7" t="n">
-        <v/>
-      </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>通常</t>
@@ -848,25 +768,10 @@
           <t>週5日</t>
         </is>
       </c>
-      <c r="F8" t="n">
-        <v/>
-      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>2026/12/29-2027/01/03</t>
         </is>
-      </c>
-      <c r="H8" t="n">
-        <v/>
-      </c>
-      <c r="I8" t="n">
-        <v/>
-      </c>
-      <c r="J8" t="n">
-        <v/>
-      </c>
-      <c r="K8" t="n">
-        <v/>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -913,18 +818,6 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="H9" t="n">
-        <v/>
-      </c>
-      <c r="I9" t="n">
-        <v/>
-      </c>
-      <c r="J9" t="n">
-        <v/>
-      </c>
-      <c r="K9" t="n">
-        <v/>
-      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>通常</t>
@@ -975,12 +868,6 @@
           <t>2026-11-10</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v/>
-      </c>
-      <c r="J10" t="n">
-        <v/>
-      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>17:30</t>
@@ -1021,19 +908,10 @@
           <t>週5日</t>
         </is>
       </c>
-      <c r="F11" t="n">
-        <v/>
-      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>2026/12/29-2027/01/03</t>
         </is>
-      </c>
-      <c r="H11" t="n">
-        <v/>
-      </c>
-      <c r="I11" t="n">
-        <v/>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1080,25 +958,10 @@
           <t>除外</t>
         </is>
       </c>
-      <c r="F12" t="n">
-        <v/>
-      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>2026/12/29-2027/01/03</t>
         </is>
-      </c>
-      <c r="H12" t="n">
-        <v/>
-      </c>
-      <c r="I12" t="n">
-        <v/>
-      </c>
-      <c r="J12" t="n">
-        <v/>
-      </c>
-      <c r="K12" t="n">
-        <v/>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1145,18 +1008,6 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="H13" t="n">
-        <v/>
-      </c>
-      <c r="I13" t="n">
-        <v/>
-      </c>
-      <c r="J13" t="n">
-        <v/>
-      </c>
-      <c r="K13" t="n">
-        <v/>
-      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>時短</t>
@@ -1192,25 +1043,10 @@
           <t>週5日</t>
         </is>
       </c>
-      <c r="F14" t="n">
-        <v/>
-      </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>2026/12/29-2027/01/03</t>
         </is>
-      </c>
-      <c r="H14" t="n">
-        <v/>
-      </c>
-      <c r="I14" t="n">
-        <v/>
-      </c>
-      <c r="J14" t="n">
-        <v/>
-      </c>
-      <c r="K14" t="n">
-        <v/>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1247,25 +1083,10 @@
           <t>週4日（必要に応じて週5日可）</t>
         </is>
       </c>
-      <c r="F15" t="n">
-        <v/>
-      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>2026/12/29-2027/01/03</t>
         </is>
-      </c>
-      <c r="H15" t="n">
-        <v/>
-      </c>
-      <c r="I15" t="n">
-        <v/>
-      </c>
-      <c r="J15" t="n">
-        <v/>
-      </c>
-      <c r="K15" t="n">
-        <v/>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1302,25 +1123,10 @@
           <t>週4日</t>
         </is>
       </c>
-      <c r="F16" t="n">
-        <v/>
-      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>2026/12/29-2027/01/03</t>
         </is>
-      </c>
-      <c r="H16" t="n">
-        <v/>
-      </c>
-      <c r="I16" t="n">
-        <v/>
-      </c>
-      <c r="J16" t="n">
-        <v/>
-      </c>
-      <c r="K16" t="n">
-        <v/>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1367,18 +1173,6 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="H17" t="n">
-        <v/>
-      </c>
-      <c r="I17" t="n">
-        <v/>
-      </c>
-      <c r="J17" t="n">
-        <v/>
-      </c>
-      <c r="K17" t="n">
-        <v/>
-      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>通常</t>
@@ -1424,19 +1218,10 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="H18" t="n">
-        <v/>
-      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>火・水・木</t>
         </is>
-      </c>
-      <c r="J18" t="n">
-        <v/>
-      </c>
-      <c r="K18" t="n">
-        <v/>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1483,19 +1268,10 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="H19" t="n">
-        <v/>
-      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>月・金・土</t>
         </is>
-      </c>
-      <c r="J19" t="n">
-        <v/>
-      </c>
-      <c r="K19" t="n">
-        <v/>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1532,25 +1308,10 @@
           <t>週5日</t>
         </is>
       </c>
-      <c r="F20" t="n">
-        <v/>
-      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>2026/12/29-2027/01/03</t>
         </is>
-      </c>
-      <c r="H20" t="n">
-        <v/>
-      </c>
-      <c r="I20" t="n">
-        <v/>
-      </c>
-      <c r="J20" t="n">
-        <v/>
-      </c>
-      <c r="K20" t="n">
-        <v/>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1597,12 +1358,6 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="H21" t="n">
-        <v/>
-      </c>
-      <c r="I21" t="n">
-        <v/>
-      </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>8:30</t>
@@ -1648,25 +1403,10 @@
           <t>週5日</t>
         </is>
       </c>
-      <c r="F22" t="n">
-        <v/>
-      </c>
       <c r="G22" t="inlineStr">
         <is>
           <t>2026/12/29-2027/01/03</t>
         </is>
-      </c>
-      <c r="H22" t="n">
-        <v/>
-      </c>
-      <c r="I22" t="n">
-        <v/>
-      </c>
-      <c r="J22" t="n">
-        <v/>
-      </c>
-      <c r="K22" t="n">
-        <v/>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1703,25 +1443,10 @@
           <t>週5日</t>
         </is>
       </c>
-      <c r="F23" t="n">
-        <v/>
-      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>2026/12/29-2027/01/03</t>
         </is>
-      </c>
-      <c r="H23" t="n">
-        <v/>
-      </c>
-      <c r="I23" t="n">
-        <v/>
-      </c>
-      <c r="J23" t="n">
-        <v/>
-      </c>
-      <c r="K23" t="n">
-        <v/>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1758,25 +1483,10 @@
           <t>週5日</t>
         </is>
       </c>
-      <c r="F24" t="n">
-        <v/>
-      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>2026/12/29-2027/01/03</t>
         </is>
-      </c>
-      <c r="H24" t="n">
-        <v/>
-      </c>
-      <c r="I24" t="n">
-        <v/>
-      </c>
-      <c r="J24" t="n">
-        <v/>
-      </c>
-      <c r="K24" t="n">
-        <v/>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1813,25 +1523,10 @@
           <t>週5日</t>
         </is>
       </c>
-      <c r="F25" t="n">
-        <v/>
-      </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>2026/12/29-2027/01/03</t>
         </is>
-      </c>
-      <c r="H25" t="n">
-        <v/>
-      </c>
-      <c r="I25" t="n">
-        <v/>
-      </c>
-      <c r="J25" t="n">
-        <v/>
-      </c>
-      <c r="K25" t="n">
-        <v/>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1878,15 +1573,6 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="H26" t="n">
-        <v/>
-      </c>
-      <c r="I26" t="n">
-        <v/>
-      </c>
-      <c r="J26" t="n">
-        <v/>
-      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>17:30</t>
@@ -1937,19 +1623,10 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="H27" t="n">
-        <v/>
-      </c>
       <c r="I27" t="inlineStr">
         <is>
           <t>月・木・金</t>
         </is>
-      </c>
-      <c r="J27" t="n">
-        <v/>
-      </c>
-      <c r="K27" t="n">
-        <v/>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -2035,9 +1712,6 @@
       <c r="E2" t="n">
         <v>1</v>
       </c>
-      <c r="F2" t="n">
-        <v/>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>HARD</t>
@@ -2068,9 +1742,6 @@
       <c r="E3" t="n">
         <v>2</v>
       </c>
-      <c r="F3" t="n">
-        <v/>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>HARD</t>
@@ -2101,9 +1772,6 @@
       <c r="E4" t="n">
         <v>1</v>
       </c>
-      <c r="F4" t="n">
-        <v/>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>HARD</t>
@@ -2134,9 +1802,6 @@
       <c r="E5" t="n">
         <v>1</v>
       </c>
-      <c r="F5" t="n">
-        <v/>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>HARD</t>
@@ -2167,9 +1832,6 @@
       <c r="E6" t="n">
         <v>1</v>
       </c>
-      <c r="F6" t="n">
-        <v/>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>HARD</t>
@@ -2200,9 +1862,6 @@
       <c r="E7" t="n">
         <v>1</v>
       </c>
-      <c r="F7" t="n">
-        <v/>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>HARD</t>
@@ -2233,9 +1892,6 @@
       <c r="E8" t="n">
         <v>2</v>
       </c>
-      <c r="F8" t="n">
-        <v/>
-      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>HARD</t>
@@ -2397,9 +2053,6 @@
       </c>
       <c r="E13" t="n">
         <v>1</v>
-      </c>
-      <c r="F13" t="n">
-        <v/>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2459,9 +2112,6 @@
           <t>重城</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v/>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2479,9 +2129,6 @@
           <t>恩田</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v/>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2499,9 +2146,6 @@
           <t>恩田</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v/>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2519,9 +2163,6 @@
           <t>恩田</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v/>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2539,9 +2180,6 @@
           <t>相原</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v/>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2559,9 +2197,6 @@
           <t>宮田</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v/>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2579,9 +2214,6 @@
           <t>真下</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v/>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2621,9 +2253,6 @@
           <t>恩田</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v/>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2641,9 +2270,6 @@
           <t>重城</t>
         </is>
       </c>
-      <c r="D11" t="n">
-        <v/>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2661,9 +2287,6 @@
           <t>恩田</t>
         </is>
       </c>
-      <c r="D12" t="n">
-        <v/>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2681,9 +2304,6 @@
           <t>真下</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v/>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2701,9 +2321,6 @@
           <t>恩田</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v/>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2743,9 +2360,6 @@
           <t>恩田</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v/>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2763,9 +2377,6 @@
           <t>恩田</t>
         </is>
       </c>
-      <c r="D17" t="n">
-        <v/>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2783,9 +2394,6 @@
           <t>恩田</t>
         </is>
       </c>
-      <c r="D18" t="n">
-        <v/>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2803,9 +2411,6 @@
           <t>恩田</t>
         </is>
       </c>
-      <c r="D19" t="n">
-        <v/>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2845,9 +2450,6 @@
           <t>恩田</t>
         </is>
       </c>
-      <c r="D21" t="n">
-        <v/>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2865,9 +2467,6 @@
           <t>恩田</t>
         </is>
       </c>
-      <c r="D22" t="n">
-        <v/>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2885,9 +2484,6 @@
           <t>真下</t>
         </is>
       </c>
-      <c r="D23" t="n">
-        <v/>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2904,9 +2500,6 @@
         <is>
           <t>恩田</t>
         </is>
-      </c>
-      <c r="D24" t="n">
-        <v/>
       </c>
     </row>
   </sheetData>
@@ -3088,8 +2681,6 @@
           <t>火</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>公</t>
@@ -3227,8 +2818,6 @@
           <t>水</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>○</t>
@@ -3366,8 +2955,6 @@
           <t>木</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>公</t>
@@ -3505,8 +3092,6 @@
           <t>金</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>○</t>
@@ -3644,8 +3229,6 @@
           <t>土</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>公</t>
@@ -3783,8 +3366,6 @@
           <t>日</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>休業</t>
@@ -3922,8 +3503,6 @@
           <t>月</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>公</t>
@@ -4061,8 +3640,6 @@
           <t>火</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>○</t>
@@ -4200,8 +3777,6 @@
           <t>水</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>公</t>
@@ -4339,8 +3914,6 @@
           <t>木</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>○</t>
@@ -4478,8 +4051,6 @@
           <t>金</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>公</t>
@@ -4617,8 +4188,6 @@
           <t>土</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>○</t>
@@ -4756,8 +4325,6 @@
           <t>日</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>休業</t>
@@ -4895,8 +4462,6 @@
           <t>月</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>○</t>
@@ -5034,8 +4599,6 @@
           <t>火</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>公</t>
@@ -5173,8 +4736,6 @@
           <t>水</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>○</t>
@@ -5312,8 +4873,6 @@
           <t>木</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>公</t>
@@ -5451,8 +5010,6 @@
           <t>金</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>○</t>
@@ -5590,8 +5147,6 @@
           <t>土</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>公</t>
@@ -5729,8 +5284,6 @@
           <t>日</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>休業</t>
@@ -5868,8 +5421,6 @@
           <t>月</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>公</t>
@@ -6007,8 +5558,6 @@
           <t>火</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>○</t>
@@ -6146,8 +5695,6 @@
           <t>水</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>公</t>
@@ -6285,8 +5832,6 @@
           <t>木</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>○</t>
@@ -6424,8 +5969,6 @@
           <t>金</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>公</t>
@@ -6563,8 +6106,6 @@
           <t>土</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>○</t>
@@ -6702,8 +6243,6 @@
           <t>日</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>○</t>
@@ -6841,8 +6380,6 @@
           <t>月</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>○</t>
@@ -6980,8 +6517,6 @@
           <t>火</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>○</t>
@@ -7119,8 +6654,6 @@
           <t>水</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>○</t>
@@ -7248,14 +6781,11 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
           <t>主公休曜日</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>土</t>
@@ -7379,6 +6909,292 @@
       <c r="AC33" t="inlineStr">
         <is>
           <t>土</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>設定項目</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>設定値</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>初期値</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>単位/選択肢</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>説明</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2階裏_基本人数</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>名</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2階裏の基本出勤人数（有休時はここから減算）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2階裏_看護師最低人数</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>名</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2階裏で絶対に欠かせない看護師の最低人数 (HARD制約)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2階裏_看護師推奨人数</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>名</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2階裏で理想とされる看護師の人数 (不足時ソフトペナルティ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>連勤上限日数</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>連続勤務の上限日数（5なら6連勤を禁止）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>固定公休_削減許容日数</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>カレンダー物理不足時の固定公休者の削減下限 (目標-N日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>3連休抑制レベル</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>強 / 中 / 弱 / なし</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>有休を除く通常の3連休発生を抑える強さ</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>セクション人数ブレ幅</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>名</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>各セクションの平均出勤人数からの許容範囲 (平均±N名)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>週休配分目標</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>7日間ローリング期間中の公休目標日数 (週休2日平準化の基準)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>既存シフト維持レベル</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>強 / 中 / 弱</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>前回の生成結果がある場合の維持の強さ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2階裏_警告表示人数</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>名以下</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Excel出力時に警告マーク(⚠️)を付ける2階裏の出勤人数</t>
         </is>
       </c>
     </row>

--- a/ope勤務条件表_2026_4sheets.xlsx
+++ b/ope勤務条件表_2026_4sheets.xlsx
@@ -1714,7 +1714,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>HARD1</t>
         </is>
       </c>
     </row>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>HIGH1</t>
         </is>
       </c>
     </row>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>HIGH2</t>
         </is>
       </c>
     </row>
@@ -1993,7 +1993,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>HIGH3</t>
         </is>
       </c>
     </row>

--- a/ope勤務条件表_2026_4sheets.xlsx
+++ b/ope勤務条件表_2026_4sheets.xlsx
@@ -6923,7 +6923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -7198,6 +7198,110 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>祝日週_公休設定</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>有効</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>有効</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>有効 / 無効</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>祝日により診療日が5日となる週に最低1日の公休を設定（5連勤防止）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>週単位_公休平準化</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>有効</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>有効</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>有効 / 無効</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>各週の公休日数を勤務パターンに応じて平準化（週4は週2日、週5は週1日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2階裏_週4名最低日数</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2階裏の通常週(6日間)における4名出勤の最低確保日数</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>空欄公休ローテーション</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>有効</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>有効</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>有効 / 無効</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>希望公休が空欄のスタッフに平日主公休を設定し月替わりでローテーション</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ope勤務条件表_2026_4sheets.xlsx
+++ b/ope勤務条件表_2026_4sheets.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,25 +463,30 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>指定公休日</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>希望出勤曜日</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>勤務開始時刻</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>勤務終了時刻</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>勤務タイプ</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>除外フラグ</t>
         </is>
@@ -518,12 +523,12 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="M2" t="b">
+      <c r="N2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -558,12 +563,12 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="M3" t="b">
+      <c r="N3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -598,17 +603,17 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>月曜出勤必須</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="M4" t="b">
+      <c r="N4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -643,17 +648,17 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>月曜出勤必須</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="M5" t="b">
+      <c r="N5" t="b">
         <v>0</v>
       </c>
     </row>
@@ -688,12 +693,12 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="M6" t="b">
+      <c r="N6" t="b">
         <v>0</v>
       </c>
     </row>
@@ -733,12 +738,12 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="M7" t="b">
+      <c r="N7" t="b">
         <v>0</v>
       </c>
     </row>
@@ -773,12 +778,12 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="M8" t="b">
+      <c r="N8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -818,12 +823,12 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="M9" t="b">
+      <c r="N9" t="b">
         <v>0</v>
       </c>
     </row>
@@ -868,17 +873,17 @@
           <t>2026-11-10</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>17:30</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="M10" t="b">
+      <c r="N10" t="b">
         <v>0</v>
       </c>
     </row>
@@ -913,22 +918,22 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>9:00</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="M11" t="b">
+      <c r="N11" t="b">
         <v>0</v>
       </c>
     </row>
@@ -963,12 +968,12 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="M12" t="b">
+      <c r="N12" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1008,12 +1013,12 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>時短</t>
         </is>
       </c>
-      <c r="M13" t="b">
+      <c r="N13" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1048,12 +1053,12 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="M14" t="b">
+      <c r="N14" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1088,12 +1093,12 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="M15" t="b">
+      <c r="N15" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1128,12 +1133,12 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="M16" t="b">
+      <c r="N16" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1173,12 +1178,12 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="M17" t="b">
+      <c r="N17" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1218,17 +1223,17 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>火・水・木</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="M18" t="b">
+      <c r="N18" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1268,17 +1273,17 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>月・金・土</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="M19" t="b">
+      <c r="N19" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1313,12 +1318,12 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="M20" t="b">
+      <c r="N20" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1358,22 +1363,22 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>8:30</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="M21" t="b">
+      <c r="N21" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1408,12 +1413,12 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="M22" t="b">
+      <c r="N22" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1448,12 +1453,12 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>時短</t>
         </is>
       </c>
-      <c r="M23" t="b">
+      <c r="N23" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1488,12 +1493,12 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="M24" t="b">
+      <c r="N24" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1528,12 +1533,12 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="M25" t="b">
+      <c r="N25" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1573,17 +1578,17 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>17:30</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="M26" t="b">
+      <c r="N26" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1623,17 +1628,17 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>月・木・金</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="M27" t="b">
+      <c r="N27" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6923,7 +6928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -7302,6 +7307,33 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>指定公休日_有効</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>有効</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>有効</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>有効 / 無効</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>スタッフマスタの指定公休日をHARD制約として強制適用</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
